--- a/data/trans_camb/IP18_E_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18_E_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 10,85</t>
+          <t>-4,86; 11,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 9,57</t>
+          <t>-5,64; 10,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-46,58; -4,72</t>
+          <t>-48,88; -3,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 14,19</t>
+          <t>-3,43; 14,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 13,45</t>
+          <t>-4,25; 12,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 21,51</t>
+          <t>-2,57; 21,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 9,99</t>
+          <t>-1,73; 10,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 9,28</t>
+          <t>-3,25; 8,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 5,31</t>
+          <t>-22,86; 5,06</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 13,4</t>
+          <t>-5,4; 13,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 11,47</t>
+          <t>-6,34; 12,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,02; -5,96</t>
+          <t>-56,14; -4,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 18,67</t>
+          <t>-3,86; 19,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 18,25</t>
+          <t>-4,91; 16,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 28,3</t>
+          <t>-2,63; 28,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 12,37</t>
+          <t>-1,96; 13,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 11,64</t>
+          <t>-3,75; 10,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 6,43</t>
+          <t>-26,91; 6,08</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 4,77</t>
+          <t>-10,36; 5,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 5,69</t>
+          <t>-11,4; 5,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-61,65; -7,92</t>
+          <t>-62,17; -8,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 7,26</t>
+          <t>-7,16; 7,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 4,61</t>
+          <t>-9,55; 5,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 4,84</t>
+          <t>-32,33; 4,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 4,11</t>
+          <t>-6,33; 4,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,26</t>
+          <t>-8,2; 2,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-35,64; -4,34</t>
+          <t>-36,45; -5,95</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 5,65</t>
+          <t>-11,35; 6,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 6,76</t>
+          <t>-12,01; 5,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,14; -8,94</t>
+          <t>-70,38; -10,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 8,39</t>
+          <t>-7,64; 8,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 5,17</t>
+          <t>-10,17; 6,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 5,63</t>
+          <t>-35,27; 4,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 4,78</t>
+          <t>-6,94; 5,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 2,47</t>
+          <t>-8,82; 2,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,86; -4,89</t>
+          <t>-39,92; -6,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 5,81</t>
+          <t>-4,55; 6,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 4,5</t>
+          <t>-7,62; 4,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 10,28</t>
+          <t>0,91; 10,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 9,32</t>
+          <t>-0,98; 9,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 5,06</t>
+          <t>-7,98; 4,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 7,74</t>
+          <t>-23,77; 7,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,75</t>
+          <t>-1,27; 6,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 3,09</t>
+          <t>-6,51; 2,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 6,4</t>
+          <t>-17,74; 6,3</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 6,27</t>
+          <t>-4,6; 7,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 4,85</t>
+          <t>-7,8; 4,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,46</t>
+          <t>0,92; 11,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 10,36</t>
+          <t>-0,97; 10,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 5,6</t>
+          <t>-8,33; 4,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 8,38</t>
+          <t>-25,0; 8,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 6,31</t>
+          <t>-1,29; 6,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,42</t>
+          <t>-6,7; 2,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 6,84</t>
+          <t>-18,44; 6,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 5,37</t>
+          <t>-1,93; 5,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,4</t>
+          <t>-2,26; 4,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 6,07</t>
+          <t>-8,61; 5,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 2,36</t>
+          <t>-4,34; 2,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,03</t>
+          <t>-1,16; 4,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 3,28</t>
+          <t>-10,12; 3,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,69</t>
+          <t>-2,3; 2,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,16</t>
+          <t>-1,22; 3,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 3,26</t>
+          <t>-6,54; 3,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,97</t>
+          <t>-1,99; 5,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,79</t>
+          <t>-2,33; 5,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 6,53</t>
+          <t>-8,96; 6,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 2,48</t>
+          <t>-4,49; 2,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,39</t>
+          <t>-1,15; 5,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 3,45</t>
+          <t>-10,5; 3,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 2,89</t>
+          <t>-2,4; 3,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,43</t>
+          <t>-1,26; 4,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 3,47</t>
+          <t>-6,84; 3,59</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,0</t>
+          <t>-2,01; 2,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,95</t>
+          <t>-1,74; 2,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 1,08</t>
+          <t>-16,57; 0,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,55</t>
+          <t>-1,51; 3,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,13</t>
+          <t>-2,48; 3,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,36</t>
+          <t>-1,36; 2,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,08</t>
+          <t>-1,62; 2,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,88</t>
+          <t>-5,02; 1,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,1</t>
+          <t>-2,01; 3,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,06</t>
+          <t>-1,76; 2,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 1,09</t>
+          <t>-16,7; 0,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,68</t>
+          <t>-1,51; 3,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,24</t>
+          <t>-2,49; 3,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,43</t>
+          <t>-1,35; 2,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,14</t>
+          <t>-1,63; 2,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,91</t>
+          <t>-5,11; 1,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 7,2</t>
+          <t>-5,67; 6,72</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 6,92</t>
+          <t>-5,06; 7,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 6,17</t>
+          <t>-25,58; 6,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 10,54</t>
+          <t>0,24; 10,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 11,15</t>
+          <t>0,49; 11,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 8,89</t>
+          <t>-19,63; 8,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 7,55</t>
+          <t>-0,66; 7,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 7,51</t>
+          <t>-0,96; 7,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 6,01</t>
+          <t>-14,39; 5,68</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 7,83</t>
+          <t>-5,72; 7,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 7,53</t>
+          <t>-5,14; 8,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 6,59</t>
+          <t>-26,28; 7,02</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 11,9</t>
+          <t>0,25; 12,2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 12,73</t>
+          <t>0,54; 13,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 9,79</t>
+          <t>-20,5; 9,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 8,29</t>
+          <t>-0,65; 7,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 8,27</t>
+          <t>-0,96; 8,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 6,51</t>
+          <t>-15,2; 6,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,6</t>
+          <t>-0,83; 3,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,71</t>
+          <t>-1,82; 2,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -3,87</t>
+          <t>-19,99; -3,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,84</t>
+          <t>-0,42; 3,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,29</t>
+          <t>-1,05; 3,34</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 4,01</t>
+          <t>-4,35; 4,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,06</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,41</t>
+          <t>-0,81; 2,43</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,48; -0,3</t>
+          <t>-9,11; -0,67</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,91</t>
+          <t>-0,88; 3,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,92</t>
+          <t>-1,93; 3,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -4,21</t>
+          <t>-21,54; -3,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,18</t>
+          <t>-0,44; 4,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,57</t>
+          <t>-1,12; 3,63</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,39</t>
+          <t>-4,65; 4,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,32</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,61</t>
+          <t>-0,86; 2,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -0,33</t>
+          <t>-9,74; -0,67</t>
         </is>
       </c>
     </row>
